--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486685_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486685_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1294</v>
+        <v>5.5638</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6645</v>
+        <v>4.9748</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4649</v>
+        <v>0.589</v>
       </c>
       <c r="G2" t="n">
         <v>4.4471</v>
@@ -610,13 +610,13 @@
         <v>0.7723</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4413</v>
+        <v>-0.0069</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3863</v>
+        <v>-0.076</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.055</v>
+        <v>0.0692</v>
       </c>
       <c r="V2" t="n">
         <v>0.3513</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0613</v>
+        <v>3.9593</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6328</v>
+        <v>4.4812</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5715</v>
+        <v>-0.5218</v>
       </c>
       <c r="G3" t="n">
         <v>1.8397</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1876</v>
+        <v>-0.2896</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4142</v>
+        <v>-0.5658</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2265</v>
+        <v>0.2762</v>
       </c>
       <c r="V3" t="n">
         <v>1.2507</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5503</v>
+        <v>2.5021</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9409</v>
+        <v>1.8927</v>
       </c>
       <c r="F4" t="n">
         <v>0.6094000000000001</v>
@@ -766,10 +766,10 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0277</v>
+        <v>-0.0759</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3038</v>
+        <v>-0.352</v>
       </c>
       <c r="U4" t="n">
         <v>0.2761</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9398</v>
+        <v>1.3047</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2443</v>
+        <v>2.1396</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3044</v>
+        <v>-0.8349</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2553</v>
+        <v>0.5289</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2688</v>
+        <v>-0.5246</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0135</v>
+        <v>1.0534</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0969</v>
+        <v>2.2128</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2831</v>
+        <v>0.7863</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8138</v>
+        <v>1.4265</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3522</v>
+        <v>-1.684</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.3109</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8003</v>
+        <v>-0.3731</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0369</v>
+        <v>-0.2206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.3589</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2098</v>
+        <v>0.1383</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3513</v>
+        <v>-0.5482</v>
       </c>
       <c r="W5" t="n">
         <v>0.2856</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.8338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.891</v>
+        <v>0.2269</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7259</v>
+        <v>0.6307</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8349</v>
+        <v>-0.4038</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5289</v>
+        <v>-0.2553</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5246</v>
+        <v>-0.2688</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0534</v>
+        <v>0.0135</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2128</v>
+        <v>1.0969</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7863</v>
+        <v>0.2831</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4265</v>
+        <v>0.8138</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.684</v>
+        <v>-1.3522</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3109</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3731</v>
+        <v>-0.8003</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5446</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6343</v>
+        <v>0.324</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7725</v>
+        <v>0.2135</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1383</v>
+        <v>0.1105</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5482</v>
+        <v>0.3513</v>
       </c>
       <c r="W6" t="n">
         <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8338</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1024</v>
+        <v>-0.0279</v>
       </c>
       <c r="E7" t="n">
         <v>0.4966</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5989</v>
+        <v>-0.5245</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2346</v>
@@ -1000,13 +1000,13 @@
         <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.447</v>
+        <v>-0.3725</v>
       </c>
       <c r="T7" t="n">
         <v>-0.4966</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2752</v>
+        <v>-0.067</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5495</v>
+        <v>-0.3909</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2743</v>
+        <v>0.324</v>
       </c>
       <c r="G8" t="n">
         <v>0.3537</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2428</v>
+        <v>-0.0345</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2759</v>
+        <v>-0.1173</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7788</v>
+        <v>-0.9553</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2892</v>
+        <v>-0.4409</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4895</v>
+        <v>-0.5144</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7931</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2098</v>
+        <v>-0.3862</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2486</v>
+        <v>-0.4003</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0389</v>
+        <v>0.014</v>
       </c>
       <c r="V9" t="n">
         <v>0.06560000000000001</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2259</v>
+        <v>-4.6396</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8956</v>
+        <v>-3.3093</v>
       </c>
       <c r="F10" t="n">
         <v>-1.3302</v>
@@ -1234,10 +1234,10 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7998</v>
+        <v>0.3862</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5239</v>
+        <v>0.1102</v>
       </c>
       <c r="U10" t="n">
         <v>0.2759</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1355</v>
+        <v>-5.9479</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6749</v>
+        <v>-4.4129</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4605</v>
+        <v>-1.535</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6133</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5185</v>
+        <v>-0.331</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6622</v>
+        <v>-0.4002</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1437</v>
+        <v>0.0692</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7759</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0053</v>
+        <v>-6.5116</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.1009</v>
+        <v>-6.632</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0956</v>
+        <v>0.1204</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4063</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8108</v>
+        <v>-0.3171</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8829</v>
+        <v>-0.414</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0721</v>
+        <v>0.0969</v>
       </c>
       <c r="V12" t="n">
         <v>1.0734</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5001</v>
+        <v>-7.3071</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5645</v>
+        <v>-5.2473</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9356</v>
+        <v>-2.0597</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9384</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.662</v>
+        <v>-0.469</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3244</v>
+        <v>-1.0072</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6624</v>
+        <v>0.5382</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5482</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.4514</v>
+        <v>-11.8996</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.369599999999999</v>
+        <v>-5.8177</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.0813</v>
+        <v>-6.0815</v>
       </c>
       <c r="G14" t="n">
         <v>-9.206799999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.103</v>
+        <v>-3.103000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.104000000000001</v>
+        <v>-6.104</v>
       </c>
       <c r="J14" t="n">
         <v>3.906400000000001</v>
@@ -1525,7 +1525,7 @@
         <v>6.211600000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.305299999999999</v>
+        <v>-2.3053</v>
       </c>
       <c r="M14" t="n">
         <v>-13.1132</v>
@@ -1537,7 +1537,7 @@
         <v>-3.7986</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0001000000000008772</v>
+        <v>-9.999999999910081e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5848</v>
@@ -1546,16 +1546,16 @@
         <v>11.5846</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3451</v>
+        <v>-1.7931</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4164</v>
+        <v>-3.8646</v>
       </c>
       <c r="U14" t="n">
         <v>2.0715</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8994000000000006</v>
+        <v>-0.8994000000000002</v>
       </c>
       <c r="W14" t="n">
         <v>5.7249</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.3589</v>
+        <v>8.969799999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.181</v>
+        <v>7.3879</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1779</v>
+        <v>1.5819</v>
       </c>
       <c r="G15" t="n">
         <v>8.059100000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2306</v>
+        <v>0.8415</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4142</v>
+        <v>-0.2073</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6448</v>
+        <v>1.0488</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.697</v>
+        <v>4.9357</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1295</v>
+        <v>4.7158</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5675</v>
+        <v>0.2199</v>
       </c>
       <c r="G16" t="n">
         <v>3.4462</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6716</v>
+        <v>0.9103</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.1927</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0652</v>
+        <v>0.7175</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9241</v>
+        <v>3.1931</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0977</v>
+        <v>-0.0058</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8264</v>
+        <v>3.1989</v>
       </c>
       <c r="G17" t="n">
         <v>2.0176</v>
@@ -1780,13 +1780,13 @@
         <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1655</v>
+        <v>0.4345</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0825</v>
+        <v>-0.0209</v>
       </c>
       <c r="U17" t="n">
-        <v>0.083</v>
+        <v>0.4555</v>
       </c>
       <c r="V17" t="n">
         <v>1.5133</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.12</v>
+        <v>1.3475</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1548</v>
+        <v>-3.0514</v>
       </c>
       <c r="F18" t="n">
-        <v>4.2748</v>
+        <v>4.399</v>
       </c>
       <c r="G18" t="n">
         <v>0.7241</v>
@@ -1858,13 +1858,13 @@
         <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3034</v>
+        <v>0.531</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3038</v>
+        <v>-0.2004</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6072</v>
+        <v>0.7313</v>
       </c>
       <c r="V18" t="n">
         <v>0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2111</v>
+        <v>0.1366</v>
       </c>
       <c r="E19" t="n">
         <v>1.6877</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4766</v>
+        <v>-1.5511</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4991</v>
@@ -1936,13 +1936,13 @@
         <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1047</v>
+        <v>-0.1792</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2815</v>
+        <v>0.2071</v>
       </c>
       <c r="V19" t="n">
         <v>0.0426</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6189</v>
+        <v>-0.2423</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2789</v>
+        <v>2.3823</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8978</v>
+        <v>-2.6246</v>
       </c>
       <c r="G20" t="n">
         <v>0.151</v>
@@ -2014,13 +2014,13 @@
         <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8938</v>
+        <v>-0.5172</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2316</v>
+        <v>0.0416</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. KOWALSKI</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6439</v>
+        <v>-1.4701</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4522</v>
+        <v>-2.1972</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8083</v>
+        <v>0.7271</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.059</v>
+        <v>-1.8534</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9868</v>
+        <v>-1.4827</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.0457</v>
+        <v>-0.3707</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3127</v>
+        <v>-0.9212</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2288</v>
+        <v>-0.2409</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.5415</v>
+        <v>-0.6803</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7462</v>
+        <v>-0.9322</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.242</v>
+        <v>-1.2418</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5042</v>
+        <v>0.3096</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8439</v>
+        <v>0.0897</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2201</v>
+        <v>-0.3106</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6237</v>
+        <v>0.4003</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5712</v>
+        <v>-0.2856</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>R. KOWALSKI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0617</v>
+        <v>-1.9086</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7143</v>
+        <v>-2.8659</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6526</v>
+        <v>0.9573</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8534</v>
+        <v>-3.059</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4827</v>
+        <v>1.9868</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3707</v>
+        <v>-5.0457</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9212</v>
+        <v>-1.3127</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2409</v>
+        <v>3.2288</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6803</v>
+        <v>-4.5415</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9322</v>
+        <v>-1.7462</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2418</v>
+        <v>-1.242</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3096</v>
+        <v>-0.5042</v>
       </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.9308</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.5792</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.5446</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-0.5019</v>
-      </c>
       <c r="T22" t="n">
-        <v>-0.8277</v>
+        <v>-0.1936</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3258</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5353</v>
+        <v>-2.5105</v>
       </c>
       <c r="E23" t="n">
         <v>-1.9719</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5634</v>
+        <v>-0.5385</v>
       </c>
       <c r="G23" t="n">
         <v>0.2205</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3696</v>
+        <v>-0.3448</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0167</v>
+        <v>0.0415</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2277</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>12.4513</v>
+        <v>12.4512</v>
       </c>
       <c r="E24" t="n">
-        <v>6.081600000000002</v>
+        <v>6.0815</v>
       </c>
       <c r="F24" t="n">
-        <v>6.369700000000002</v>
+        <v>6.369899999999999</v>
       </c>
       <c r="G24" t="n">
         <v>9.207000000000003</v>
@@ -2332,7 +2332,7 @@
         <v>-2.0715</v>
       </c>
       <c r="U24" t="n">
-        <v>4.4163</v>
+        <v>4.416300000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.8994000000000004</v>
